--- a/copilot/examples/03_power_query.xlsx
+++ b/copilot/examples/03_power_query.xlsx
@@ -1167,10 +1167,11 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>This example's Power Queries, which the tool that made this file can't save in it. To see the workbook as it should be, add each in Excel: Data &gt; Get Data &gt; From Other Sources &gt; Blank Query, Home &gt; Advanced Editor, paste its M, name it as below, then Close &amp; Load To &gt; Only Create Connection. Then, in the Queries &amp; Connections pane, right-click it, Load To, and pick the existing Table of its name, which it then fills.</t>
-        </is>
-      </c>
-    </row>
+          <t>This example's Power Queries, which the tool that made this file can't save in it, so the Tables ok_runs and ok_by_job hold the rows the queries give, typed in. To see the workbook as it should be, add each query in Excel, in order: Data &gt; Get Data &gt; From Other Sources &gt; Blank Query, Home &gt; Advanced Editor, paste its M below, and name it as below. On the sheet of its name, delete the typed-in Table (select it and press Delete, then delete the empty Table), then Home &gt; Close &amp; Load To &gt; Table, at A1 of that sheet. For ok_runs, type the formula column again beside the loaded rows: hours, =[@duration_mins]/60. Excel keeps it when the query refreshes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1190,6 +1191,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1235,17 +1237,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What Copilot gives with files 11 and 12 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet before you try the workbook on Copilot yourself.</t>
-        </is>
-      </c>
-    </row>
+          <t>What Copilot gives with files 11, 12, 03, 04 and 05 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet, and the Power Query sheet if there is one, before you try the workbook on Copilot yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sources: job_runs. Steps: query ok_runs, a CTE in each final that reads it, as query ok_by_job reads it. Finals: Table ok_runs (run_id, job_id, duration_mins, hours), its query's rows and its formula column, as no formula reads that Table; Table ok_by_job (job_id, total_mins). Fill in: &lt;database&gt;.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sources: job_runs. Steps: query ok_runs, as query ok_by_job reads it, so it is a CTE in each final's query. Finals: Table ok_runs (run_id, job_id, duration_mins, hours): query ok_by_job reads the query, not the Table, and no formula reads the Table, so it is a final, its query's rows and its hours column; Table ok_by_job (job_id, total_mins). Fill in: &lt;database&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1262,6 +1266,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
